--- a/docs/评估集_结果.xlsx
+++ b/docs/评估集_结果.xlsx
@@ -38,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +53,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -91,6 +96,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -458,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2760,7 +2768,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>2025Q4分吞吐量级服务测评里，4000万级以上机场综合得分前两名是谁</t>
+          <t>2025Q4分吞吐量级服务测评的表格里，红色和蓝色分别代表什么</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2770,7 +2778,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>北京大兴国际机场4.28；深圳宝安国际机场4.27。</t>
+          <t>红色为高于行业平均分，蓝色为低于行业平均分，下同。</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2801,12 +2809,16 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>出处存在;你写的数 ['4.27', '4.28'] 原文里都有</t>
+          <t>出处存在;没写数字,只摆原文</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>检索：分吞吐量级文本</t>
+          <t>检索：分吞吐量级表格的【排版约定】。
+★ 这条【只能从原文读】—— 库里的 机场分档 表有档位和平均分,
+  但没有"红色/蓝色代表什么"(那是"这张表怎么读"的说明)。
+★ 改动理由(2026-10-01):原来问的是"4000万级以上前两名是谁",
+  而那个【库里能算】—— 考检索是白考。换成这一句,它才重新变成能区分好坏的题。</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2828,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>叙述·检索</t>
+          <t>数值·排名</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2826,7 +2838,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>检索</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2853,19 +2865,23 @@
 4.11 平均, 4.15厦门高崎国际机场南京禄口国际机场青岛胶东国际机场武汉天河国际机场成都双流国际机场长沙黄花国际机场乌鲁木齐天山国际机场郑州新郑国际机场海口美兰国际机场</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>✅可核</t>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>出处存在;你写的数 ['4.25'] 原文里都有</t>
+          <t>去向填的是 SQL,但出处指向 chunk(原文)—— 你到底要哪个?</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>检索：分吞吐量级文本</t>
+          <t>检索：分吞吐量级文本
+★ 2026-10-01 改:期望去向 检索→SQL,类别 叙述·检索→数值·排名。
+理由:这题问的是"某一档里第一是谁",而库里有 `机场分档` 表(4 个档),
+SQL 能直接算出来。★ 检索那条路拿到的是一串孤立数字(表格结构丢了),
+配不上对。★ 判据:「能算的地方,别去检索里翻」。</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2891,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>叙述·检索</t>
+          <t>数值·排名</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2885,7 +2901,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>检索</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2915,19 +2931,23 @@
 4.05平均, 4.15无锡硕放国际机场宁波栎社国际机场温州龙湾国际机场银川河东国际机场烟台蓬莱国际机场石家庄正定国际机场呼和浩特白塔国际机场珠海金湾机场合肥新桥国际机场南宁吴圩国际机场南昌昌北国际机场太原武宿国际机场</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>✅可核</t>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>出处存在;你写的数 ['4.17'] 原文里都有</t>
+          <t>去向填的是 SQL,但出处指向 chunk(原文)—— 你到底要哪个?</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>检索：分吞吐量级并列</t>
+          <t>检索：分吞吐量级并列
+★ 2026-10-01 改:期望去向 检索→SQL,类别 叙述·检索→数值·排名。
+理由:这题问的是"某一档里第一是谁",而库里有 `机场分档` 表(4 个档),
+SQL 能直接算出来。★ 检索那条路拿到的是一串孤立数字(表格结构丢了),
+配不上对。★ 判据:「能算的地方,别去检索里翻」。</t>
         </is>
       </c>
     </row>
@@ -3506,6 +3526,1562 @@
       <c r="J61" s="2" t="inlineStr">
         <is>
           <t>边界：已知缺口</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>条件·多步</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>分析浦东近两期，如果降了就查原因，没降就看看它和同档平均水平比怎么样</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>2025Q3 上海浦东国际机场 4.23；2025Q4 上海浦东国际机场 4.23；两期持平（没降）；同档平均 4.13；上海浦东国际机场 比同档平均 高 0.1</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>2025Q4-P09 / 2025Q4-P18</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>[2025Q4-P09 = 2025Q4 第 9 页] 北京大兴国际机场 4.28
+深圳宝安国际机场 4.27
+上海虹桥国际机场 4.25
+厦门高崎国际机场 4.25
+上海浦东国际机场 4.23
+南京禄口国际机场 4.22
+青岛胶东国际机场 4.22
+重庆江北国际机场 4.21
+武汉天河国际机场 4.21
+广州白云国际机场 4.20
+成都天府国际机场 4.20
+成都双流国际机场 4.20
+杭州萧山国际机场 4.19
+西安咸阳国际机场 4.18
+无锡硕放国际机场 4.17
+宁波栎社国际机场 4.17
+沈阳桃仙国际机场 4.16
+大连国际机场 4.16
+福州长乐国际机场 4.16
+长沙黄花国际机场 4.15
+乌鲁木齐天山国际机场 4.15
+北京首都国际机场 4.14
+郑州新郑国际机场 4.14
+昆明长水国际机场 4.13
+天津滨海国际机场 4.13
+贵阳龙洞堡国际机场 4.13
+温州龙湾国际机场 4.13
+银川河东国际机场 4.12
+烟台蓬莱国际机场 4.12
+济南遥墙国际机场 4.12
+石家庄正定国际机场 4.11
+呼和浩特白塔国际机场 4.11
+海口美兰国际机场 4.11
+珠海金湾机场 4.10
+长春龙嘉国际机场 4.10
+哈尔滨太平国际机场 4.10
+兰州中川国际机场 4.10
+三亚凤凰国际机场 4.09
+合肥新桥国际机场 4.09
+南宁吴圩国际机场 4.08
+南昌昌北国际机场 4.05
+太原武宿国际机场 4.05</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>去向填的是 SQL,但出处指向 chunk(原文)—— 你到底要哪个?</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>★ 带条件：该判降没降，再只走【它走到的那一支】。★ 期望答案由 AI 起草、待用户审。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>条件·多步</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>浦东2025Q4表现怎么样，要是不好就说说是哪一项拖后腿</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>2025Q4 上海浦东国际机场 综合得分 4.23；排名第 5；★ 并【说清】「要是不好就说说是哪一项拖后腿」这一件【没答】——那一件该出声，不该静默（AI 起草、待用户审）</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>2025Q4-P09</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>[2025Q4-P09 = 2025Q4 第 9 页] 北京大兴国际机场 4.28
+深圳宝安国际机场 4.27
+上海虹桥国际机场 4.25
+厦门高崎国际机场 4.25
+上海浦东国际机场 4.23
+南京禄口国际机场 4.22
+青岛胶东国际机场 4.22
+重庆江北国际机场 4.21
+武汉天河国际机场 4.21
+广州白云国际机场 4.20
+成都天府国际机场 4.20
+成都双流国际机场 4.20
+杭州萧山国际机场 4.19
+西安咸阳国际机场 4.18
+无锡硕放国际机场 4.17
+宁波栎社国际机场 4.17
+沈阳桃仙国际机场 4.16
+大连国际机场 4.16
+福州长乐国际机场 4.16
+长沙黄花国际机场 4.15
+乌鲁木齐天山国际机场 4.15
+北京首都国际机场 4.14
+郑州新郑国际机场 4.14
+昆明长水国际机场 4.13
+天津滨海国际机场 4.13
+贵阳龙洞堡国际机场 4.13
+温州龙湾国际机场 4.13
+银川河东国际机场 4.12
+烟台蓬莱国际机场 4.12
+济南遥墙国际机场 4.12
+石家庄正定国际机场 4.11
+呼和浩特白塔国际机场 4.11
+海口美兰国际机场 4.11
+珠海金湾机场 4.10
+长春龙嘉国际机场 4.10
+哈尔滨太平国际机场 4.10
+兰州中川国际机场 4.10
+三亚凤凰国际机场 4.09
+合肥新桥国际机场 4.09
+南宁吴圩国际机场 4.08
+南昌昌北国际机场 4.05
+太原武宿国际机场 4.05</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>去向填的是 SQL,但出处指向 chunk(原文)—— 你到底要哪个?</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>★ 条件藏在字缝里（没有“如果”两字）。★ “哪一项拖后腿”这一件【答不了】—— 该【说出来】，不该静默。期望答案由 AI 起草、待审。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>条件·多步</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>浦东和虹桥2025Q4谁高，低的那家差在哪</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>上海浦东国际机场 4.23；上海虹桥国际机场 4.25；上海虹桥国际机场 更高（4.25 比 4.23）</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>2025Q4-P09</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>[2025Q4-P09 = 2025Q4 第 9 页] 北京大兴国际机场 4.28
+深圳宝安国际机场 4.27
+上海虹桥国际机场 4.25
+厦门高崎国际机场 4.25
+上海浦东国际机场 4.23
+南京禄口国际机场 4.22
+青岛胶东国际机场 4.22
+重庆江北国际机场 4.21
+武汉天河国际机场 4.21
+广州白云国际机场 4.20
+成都天府国际机场 4.20
+成都双流国际机场 4.20
+杭州萧山国际机场 4.19
+西安咸阳国际机场 4.18
+无锡硕放国际机场 4.17
+宁波栎社国际机场 4.17
+沈阳桃仙国际机场 4.16
+大连国际机场 4.16
+福州长乐国际机场 4.16
+长沙黄花国际机场 4.15
+乌鲁木齐天山国际机场 4.15
+北京首都国际机场 4.14
+郑州新郑国际机场 4.14
+昆明长水国际机场 4.13
+天津滨海国际机场 4.13
+贵阳龙洞堡国际机场 4.13
+温州龙湾国际机场 4.13
+银川河东国际机场 4.12
+烟台蓬莱国际机场 4.12
+济南遥墙国际机场 4.12
+石家庄正定国际机场 4.11
+呼和浩特白塔国际机场 4.11
+海口美兰国际机场 4.11
+珠海金湾机场 4.10
+长春龙嘉国际机场 4.10
+哈尔滨太平国际机场 4.10
+兰州中川国际机场 4.10
+三亚凤凰国际机场 4.09
+合肥新桥国际机场 4.09
+南宁吴圩国际机场 4.08
+南昌昌北国际机场 4.05
+太原武宿国际机场 4.05</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>去向填的是 SQL,但出处指向 chunk(原文)—— 你到底要哪个?</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>★ 要先算出来才知道“低的那家”指谁——句子里没有“如果”，可它照样是岔路口。★ 期望答案由 AI 起草、待审。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>条件·多步</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>浦东2025Q4综合得分是多少</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>2025Q4 上海浦东国际机场 综合得分 4.23</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>2025Q4-P09</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>[2025Q4-P09 = 2025Q4 第 9 页] 北京大兴国际机场 4.28
+深圳宝安国际机场 4.27
+上海虹桥国际机场 4.25
+厦门高崎国际机场 4.25
+上海浦东国际机场 4.23
+南京禄口国际机场 4.22
+青岛胶东国际机场 4.22
+重庆江北国际机场 4.21
+武汉天河国际机场 4.21
+广州白云国际机场 4.20
+成都天府国际机场 4.20
+成都双流国际机场 4.20
+杭州萧山国际机场 4.19
+西安咸阳国际机场 4.18
+无锡硕放国际机场 4.17
+宁波栎社国际机场 4.17
+沈阳桃仙国际机场 4.16
+大连国际机场 4.16
+福州长乐国际机场 4.16
+长沙黄花国际机场 4.15
+乌鲁木齐天山国际机场 4.15
+北京首都国际机场 4.14
+郑州新郑国际机场 4.14
+昆明长水国际机场 4.13
+天津滨海国际机场 4.13
+贵阳龙洞堡国际机场 4.13
+温州龙湾国际机场 4.13
+银川河东国际机场 4.12
+烟台蓬莱国际机场 4.12
+济南遥墙国际机场 4.12
+石家庄正定国际机场 4.11
+呼和浩特白塔国际机场 4.11
+海口美兰国际机场 4.11
+珠海金湾机场 4.10
+长春龙嘉国际机场 4.10
+哈尔滨太平国际机场 4.10
+兰州中川国际机场 4.10
+三亚凤凰国际机场 4.09
+合肥新桥国际机场 4.09
+南宁吴圩国际机场 4.08
+南昌昌北国际机场 4.05
+太原武宿国际机场 4.05</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>去向填的是 SQL,但出处指向 chunk(原文)—— 你到底要哪个?</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>★★ 反向题：问一个数，【不该】走任何条件分支、不该展开。★ 没有它，一个“什么都当条件处理”的实现也能把前几道蒙对。期望答案由 AI 起草、待审。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>条件·多步</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>浦东2025Q4排第几，前三名是谁</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>上海浦东国际机场 排名第 5；前三名：北京大兴国际机场 4.28、深圳宝安国际机场 4.27、上海虹桥国际机场 4.25</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>2025Q4-P09</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>[2025Q4-P09 = 2025Q4 第 9 页] 北京大兴国际机场 4.28
+深圳宝安国际机场 4.27
+上海虹桥国际机场 4.25
+厦门高崎国际机场 4.25
+上海浦东国际机场 4.23
+南京禄口国际机场 4.22
+青岛胶东国际机场 4.22
+重庆江北国际机场 4.21
+武汉天河国际机场 4.21
+广州白云国际机场 4.20
+成都天府国际机场 4.20
+成都双流国际机场 4.20
+杭州萧山国际机场 4.19
+西安咸阳国际机场 4.18
+无锡硕放国际机场 4.17
+宁波栎社国际机场 4.17
+沈阳桃仙国际机场 4.16
+大连国际机场 4.16
+福州长乐国际机场 4.16
+长沙黄花国际机场 4.15
+乌鲁木齐天山国际机场 4.15
+北京首都国际机场 4.14
+郑州新郑国际机场 4.14
+昆明长水国际机场 4.13
+天津滨海国际机场 4.13
+贵阳龙洞堡国际机场 4.13
+温州龙湾国际机场 4.13
+银川河东国际机场 4.12
+烟台蓬莱国际机场 4.12
+济南遥墙国际机场 4.12
+石家庄正定国际机场 4.11
+呼和浩特白塔国际机场 4.11
+海口美兰国际机场 4.11
+珠海金湾机场 4.10
+长春龙嘉国际机场 4.10
+哈尔滨太平国际机场 4.10
+兰州中川国际机场 4.10
+三亚凤凰国际机场 4.09
+合肥新桥国际机场 4.09
+南宁吴圩国际机场 4.08
+南昌昌北国际机场 4.05
+太原武宿国际机场 4.05</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>去向填的是 SQL,但出处指向 chunk(原文)—— 你到底要哪个?</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>★ 两步、不是分支——两件都必然要答。★ 而实测主链答不了“前三名” → 该【说出来】。期望答案由 AI 起草、待审。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>条件·多步</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>2025Q4合肥新桥国际机场排第几，最后一名是谁</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>合肥新桥国际机场 排名第 39；最后一名（第42名）太原武宿国际机场 4.05</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>2025Q4-P09</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>[2025Q4-P09 = 2025Q4 第 9 页] 北京大兴国际机场 4.28
+深圳宝安国际机场 4.27
+上海虹桥国际机场 4.25
+厦门高崎国际机场 4.25
+上海浦东国际机场 4.23
+南京禄口国际机场 4.22
+青岛胶东国际机场 4.22
+重庆江北国际机场 4.21
+武汉天河国际机场 4.21
+广州白云国际机场 4.20
+成都天府国际机场 4.20
+成都双流国际机场 4.20
+杭州萧山国际机场 4.19
+西安咸阳国际机场 4.18
+无锡硕放国际机场 4.17
+宁波栎社国际机场 4.17
+沈阳桃仙国际机场 4.16
+大连国际机场 4.16
+福州长乐国际机场 4.16
+长沙黄花国际机场 4.15
+乌鲁木齐天山国际机场 4.15
+北京首都国际机场 4.14
+郑州新郑国际机场 4.14
+昆明长水国际机场 4.13
+天津滨海国际机场 4.13
+贵阳龙洞堡国际机场 4.13
+温州龙湾国际机场 4.13
+银川河东国际机场 4.12
+烟台蓬莱国际机场 4.12
+济南遥墙国际机场 4.12
+石家庄正定国际机场 4.11
+呼和浩特白塔国际机场 4.11
+海口美兰国际机场 4.11
+珠海金湾机场 4.10
+长春龙嘉国际机场 4.10
+哈尔滨太平国际机场 4.10
+兰州中川国际机场 4.10
+三亚凤凰国际机场 4.09
+合肥新桥国际机场 4.09
+南宁吴圩国际机场 4.08
+南昌昌北国际机场 4.05
+太原武宿国际机场 4.05</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>去向填的是 SQL,但出处指向 chunk(原文)—— 你到底要哪个?</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>★ 两步、两件都必然要答。★ 第二件【要去补】,不该只说「我没答」。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>条件·多步</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>2025Q3广州白云国际机场综合得分是多少，排名第几</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>2025Q3 广州白云国际机场 综合得分 4.21；排名第 9</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>2025Q3-P09</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>[2025Q3-P09 = 2025Q3 第 9 页] 北京大兴国际机场 4.30
+深圳宝安国际机场 4.27
+上海虹桥国际机场 4.26
+厦门高崎国际机场 4.24
+南京禄口国际机场 4.23
+上海浦东国际机场 4.23
+重庆江北国际机场 4.22
+青岛胶东国际机场 4.22
+武汉天河国际机场 4.21
+广州白云国际机场 4.21
+成都天府国际机场 4.20
+杭州萧山国际机场 4.19
+成都双流国际机场 4.19
+西安咸阳国际机场 4.19
+无锡硕放国际机场 4.17
+福州长乐国际机场 4.17
+宁波栎社国际机场 4.16
+乌鲁木齐天山国际机场 4.16
+长沙黄花国际机场 4.15
+沈阳桃仙国际机场 4.15
+北京首都国际机场 4.15
+大连国际机场 4.14
+郑州新郑国际机场 4.13
+济南遥墙国际机场 4.13
+昆明长水国际机场 4.13
+贵阳龙洞堡国际机场 4.12
+天津滨海国际机场 4.12
+烟台蓬莱国际机场 4.11
+温州龙湾国际机场 4.11
+珠海金湾机场 4.11
+海口美兰国际机场 4.10
+呼和浩特白塔国际机场 4.10
+长春龙嘉国际机场 4.10
+银川河东国际机场 4.10
+合肥新桥国际机场 4.09
+哈尔滨太平国际机场 4.09
+兰州中川国际机场 4.09
+三亚凤凰国际机场 4.09
+石家庄正定国际机场 4.08
+南宁吴圩国际机场 4.07
+太原武宿国际机场 4.04
+南昌昌北国际机场 4.02</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>去向填的是 SQL,但出处指向 chunk(原文)—— 你到底要哪个?</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>★ 两件都在同一句里,而一件是【数值】、一件是【排名】—— 看它能不能两件都做。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>数值·排名</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>2025Q4分吞吐量级服务测评里，4000万级以上机场综合得分第一是谁</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>北京大兴国际机场 4.28（2025Q4 4000万级以上机场综合得分第一）</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>chunk=2025Q4-P18</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>[2025Q4-P18 = 2025Q4 第 18 页] ◆机场综合得分包含测评项目：机场交通、机场服务与设施、机场商贸、机场安检、出港服务、进港服务、航班不正常保障。2025Q4—4000万级以上机场综合得分备注：红色为高于行业平均分，蓝色为低于行业平均分，下同。
+4.28
+4.27
+4.25
+4.23
+4.21
+4.20
+4.20
+4.19
+4.18
+4.14
+4.13 平均, 4.15北京大兴国际机场深圳宝安国际机场上海虹桥国际机场上海浦东国际机场重庆江北国际机场广州白云国际机场成都天府国际机场杭州萧山国际机场西安咸阳国际机场北京首都国际机场昆明长水国际机场</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>去向填的是 SQL,但出处指向 chunk(原文)—— 你到底要哪个?</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>★★ 假复合 —— 逗号【不是分句】,前半段「2025Q4分吞吐量级服务测评里」是【状语】。★ 补漏【不该】把它当成一件去补,也不该报「漏了」。#48 就是这个形状的误报。（AI 起草、待用户审）
+★ 2026-10-01 改:期望去向 检索→SQL,类别 叙述·检索→数值·排名。
+理由:这题问的是"某一档里第一是谁",而库里有 `机场分档` 表(4 个档),
+SQL 能直接算出来。★ 检索那条路拿到的是一串孤立数字(表格结构丢了),
+配不上对。★ 判据:「能算的地方,别去检索里翻」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>条件·多步</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>浦东和虹桥2025Q4谁高，各自排第几</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>上海虹桥国际机场 4.25 高于 上海浦东国际机场 4.23；虹桥排第 3、浦东排第 5</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>2025Q4-P09</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>[2025Q4-P09 = 2025Q4 第 9 页] 北京大兴国际机场 4.28
+深圳宝安国际机场 4.27
+上海虹桥国际机场 4.25
+厦门高崎国际机场 4.25
+上海浦东国际机场 4.23
+南京禄口国际机场 4.22
+青岛胶东国际机场 4.22
+重庆江北国际机场 4.21
+武汉天河国际机场 4.21
+广州白云国际机场 4.20
+成都天府国际机场 4.20
+成都双流国际机场 4.20
+杭州萧山国际机场 4.19
+西安咸阳国际机场 4.18
+无锡硕放国际机场 4.17
+宁波栎社国际机场 4.17
+沈阳桃仙国际机场 4.16
+大连国际机场 4.16
+福州长乐国际机场 4.16
+长沙黄花国际机场 4.15
+乌鲁木齐天山国际机场 4.15
+北京首都国际机场 4.14
+郑州新郑国际机场 4.14
+昆明长水国际机场 4.13
+天津滨海国际机场 4.13
+贵阳龙洞堡国际机场 4.13
+温州龙湾国际机场 4.13
+银川河东国际机场 4.12
+烟台蓬莱国际机场 4.12
+济南遥墙国际机场 4.12
+石家庄正定国际机场 4.11
+呼和浩特白塔国际机场 4.11
+海口美兰国际机场 4.11
+珠海金湾机场 4.10
+长春龙嘉国际机场 4.10
+哈尔滨太平国际机场 4.10
+兰州中川国际机场 4.10
+三亚凤凰国际机场 4.09
+合肥新桥国际机场 4.09
+南宁吴圩国际机场 4.08
+南昌昌北国际机场 4.05
+太原武宿国际机场 4.05</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>去向填的是 SQL,但出处指向 chunk(原文)—— 你到底要哪个?</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>★ 第二段「各自排第几」【不带机场名】—— 得靠第一段继承。★ 测补漏时的【参数传承】。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>条件·多步</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>比较北京大兴和上海浦东2025Q3和2025Q4的综合得分变化，如果下降了就去找原因</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>北京大兴国际机场 4.3 → 4.28（下降了）；上海浦东国际机场 4.23 → 4.23（持平）。所以只有北京大兴下降</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>2025Q3-P09 | 2025Q4-P09</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>[2025Q3-P09 = 2025Q3 第 9 页] 北京大兴国际机场 4.30
+深圳宝安国际机场 4.27
+上海虹桥国际机场 4.26
+厦门高崎国际机场 4.24
+南京禄口国际机场 4.23
+上海浦东国际机场 4.23
+重庆江北国际机场 4.22
+青岛胶东国际机场 4.22
+武汉天河国际机场 4.21
+广州白云国际机场 4.21
+成都天府国际机场 4.20
+杭州萧山国际机场 4.19
+成都双流国际机场 4.19
+西安咸阳国际机场 4.19
+无锡硕放国际机场 4.17
+福州长乐国际机场 4.17
+宁波栎社国际机场 4.16
+乌鲁木齐天山国际机场 4.16
+长沙黄花国际机场 4.15
+沈阳桃仙国际机场 4.15
+北京首都国际机场 4.15
+大连国际机场 4.14
+郑州新郑国际机场 4.13
+济南遥墙国际机场 4.13
+昆明长水国际机场 4.13
+贵阳龙洞堡国际机场 4.12
+天津滨海国际机场 4.12
+烟台蓬莱国际机场 4.11
+温州龙湾国际机场 4.11
+珠海金湾机场 4.11
+海口美兰国际机场 4.10
+呼和浩特白塔国际机场 4.10
+长春龙嘉国际机场 4.10
+银川河东国际机场 4.10
+合肥新桥国际机场 4.09
+哈尔滨太平国际机场 4.09
+兰州中川国际机场 4.09
+三亚凤凰国际机场 4.09
+石家庄正定国际机场 4.08
+南宁吴圩国际机场 4.07
+太原武宿国际机场 4.04
+南昌昌北国际机场 4.02</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>去向填的是 SQL,但出处指向 chunk(原文)—— 你到底要哪个?</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>★★ 多步 + 条件 —— 触发点在第3步:那时结果里已有【两步】,而条件里的两个量来自【第1步的两条】。★ 现有所有条件题的判据场景都是"两个量来自两个不同步骤",这一道撞那个缺口。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>歧义·反问</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>三亚凤凰国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>反问</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>该反问:极值词有两种读法,两种答案不同</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="n"/>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>去向只能填 SQL/检索/拒答,你填的是 '反问'</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的,不是我编的 —— 见 tools/枚举歧义.py。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="28" customHeight="1">
+      <c r="A73" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>歧义·反问</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>上海浦东国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>反问</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>该反问:极值词有两种读法,两种答案不同</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="n"/>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>去向只能填 SQL/检索/拒答,你填的是 '反问'</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的,不是我编的 —— 见 tools/枚举歧义.py。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="28" customHeight="1">
+      <c r="A74" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>歧义·反问</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>上海虹桥国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>反问</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>该反问:极值词有两种读法,两种答案不同</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="n"/>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>去向只能填 SQL/检索/拒答,你填的是 '反问'</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的,不是我编的 —— 见 tools/枚举歧义.py。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="28" customHeight="1">
+      <c r="A75" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>歧义·反问</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>乌鲁木齐天山国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>反问</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>该反问:极值词有两种读法,两种答案不同</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="n"/>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>去向只能填 SQL/检索/拒答,你填的是 '反问'</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的,不是我编的 —— 见 tools/枚举歧义.py。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="28" customHeight="1">
+      <c r="A76" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>歧义·反问</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>北京大兴国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>反问</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>该反问:极值词有两种读法,两种答案不同</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="n"/>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>去向只能填 SQL/检索/拒答,你填的是 '反问'</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的,不是我编的 —— 见 tools/枚举歧义.py。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="28" customHeight="1">
+      <c r="A77" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>歧义·反问</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>北京首都国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>反问</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>该反问:极值词有两种读法,两种答案不同</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="n"/>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>去向只能填 SQL/检索/拒答,你填的是 '反问'</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的,不是我编的 —— 见 tools/枚举歧义.py。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="28" customHeight="1">
+      <c r="A78" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>歧义·反问</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>南京禄口国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>反问</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>该反问:极值词有两种读法,两种答案不同</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="n"/>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>去向只能填 SQL/检索/拒答,你填的是 '反问'</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的,不是我编的 —— 见 tools/枚举歧义.py。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="28" customHeight="1">
+      <c r="A79" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>歧义·反问</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>南宁吴圩国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>反问</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>该反问:极值词有两种读法,两种答案不同</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="n"/>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>去向只能填 SQL/检索/拒答,你填的是 '反问'</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的,不是我编的 —— 见 tools/枚举歧义.py。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="28" customHeight="1">
+      <c r="A80" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>歧义·该答</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>兰州中川国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>兰州中川国际机场 2025Q4 一级指标里最低的是「航班不正常保障」2.88</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="n"/>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>出处读不懂 —— 出处是空的</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的（见 tools/枚举歧义.py）。★ 这道是【乙类】:两种读法指向同一个指标,所以【不该反问,直接答】。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="28" customHeight="1">
+      <c r="A81" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>歧义·该答</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>呼和浩特白塔国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>呼和浩特白塔国际机场 2025Q4 一级指标里最低的是「航班不正常保障」2.91</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="n"/>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>出处读不懂 —— 出处是空的</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的（见 tools/枚举歧义.py）。★ 这道是【乙类】:两种读法指向同一个指标,所以【不该反问,直接答】。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="28" customHeight="1">
+      <c r="A82" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>歧义·该答</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>哈尔滨太平国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>哈尔滨太平国际机场 2025Q4 一级指标里最低的是「航班不正常保障」3.02</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="n"/>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>出处读不懂 —— 出处是空的</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的（见 tools/枚举歧义.py）。★ 这道是【乙类】:两种读法指向同一个指标,所以【不该反问,直接答】。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="28" customHeight="1">
+      <c r="A83" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>歧义·该答</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>宁波栎社国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>宁波栎社国际机场 2025Q4 一级指标里最低的是「航班不正常保障」3.05</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="n"/>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>出处读不懂 —— 出处是空的</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的（见 tools/枚举歧义.py）。★ 这道是【乙类】:两种读法指向同一个指标,所以【不该反问,直接答】。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="28" customHeight="1">
+      <c r="A84" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>歧义·该答</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>成都天府国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>成都天府国际机场 2025Q4 一级指标里最低的是「航班不正常保障」3.18</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="n"/>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>出处读不懂 —— 出处是空的</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的（见 tools/枚举歧义.py）。★ 这道是【乙类】:两种读法指向同一个指标,所以【不该反问,直接答】。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="28" customHeight="1">
+      <c r="A85" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>歧义·该答</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>昆明长水国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>昆明长水国际机场 2025Q4 一级指标里最低的是「航班不正常保障」3.09</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="n"/>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>出处读不懂 —— 出处是空的</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的（见 tools/枚举歧义.py）。★ 这道是【乙类】:两种读法指向同一个指标,所以【不该反问,直接答】。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="28" customHeight="1">
+      <c r="A86" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>歧义·该答</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>杭州萧山国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>杭州萧山国际机场 2025Q4 一级指标里最低的是「航班不正常保障」3.25</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="n"/>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>出处读不懂 —— 出处是空的</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的（见 tools/枚举歧义.py）。★ 这道是【乙类】:两种读法指向同一个指标,所以【不该反问,直接答】。（AI 起草、待用户审）</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="28" customHeight="1">
+      <c r="A87" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>歧义·该答</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>郑州新郑国际机场2025Q4哪一项指标最弱</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>郑州新郑国际机场 2025Q4 一级指标里最低的是「航班不正常保障」2.93</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="n"/>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>★格式</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>出处读不懂 —— 出处是空的</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>★★ 从库里枚举出来的（见 tools/枚举歧义.py）。★ 这道是【乙类】:两种读法指向同一个指标,所以【不该反问,直接答】。（AI 起草、待用户审）</t>
         </is>
       </c>
     </row>
